--- a/backtest_runs/20260410_193731/by_symbol/DSL/DSL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DSL/DSL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-6934.239999999998</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>93065.76000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>97992.72000000002</v>
@@ -771,7 +771,7 @@
         <v>-1459.840000000001</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>108394.08</v>
@@ -817,7 +817,7 @@
         <v>-2554.719999999994</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>105839.36</v>
@@ -909,7 +909,7 @@
         <v>-1824.80000000001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>107664.16</v>
@@ -955,7 +955,7 @@
         <v>-1642.319999999997</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>106021.84</v>
@@ -1001,7 +1001,7 @@
         <v>-182.4799999999961</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>105839.36</v>
@@ -1047,7 +1047,7 @@
         <v>-364.9599999999922</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>105474.4</v>
@@ -1093,7 +1093,7 @@
         <v>-1094.880000000009</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>104379.52</v>
@@ -1185,7 +1185,7 @@
         <v>-3284.640000000011</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>104562</v>
@@ -1231,7 +1231,7 @@
         <v>-364.9599999999922</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>104197.04</v>
@@ -1415,7 +1415,7 @@
         <v>-3467.119999999991</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>104014.56</v>
@@ -1461,7 +1461,7 @@
         <v>-912.4000000000129</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>103102.16</v>
@@ -1645,7 +1645,7 @@
         <v>-4562</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>106751.76</v>
